--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_387_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_387_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>63:52</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
     </row>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48:20</t>
+          <t>27:27</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -1923,10 +1923,10 @@
         <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>24:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -2511,16 +2511,16 @@
         <v>14</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>6</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>54:19</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -2710,13 +2710,13 @@
         <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>7</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>36:30</t>
+          <t>25:36</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -3295,7 +3295,7 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>56:02</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>41:57</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>84</v>
       </c>
       <c r="T30" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>27</v>
@@ -4292,10 +4292,10 @@
         <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>51:59</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>42:06</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,22 +4604,22 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>57:52</t>
+          <t>26:59</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>47:48</t>
+          <t>26:55</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>74:31</t>
+          <t>33:38</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -5468,10 +5468,10 @@
         <v>19</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>35:30</t>
+          <t>24:37</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,22 +5584,22 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -6252,16 +6252,16 @@
         <v>12</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>2</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>50:19</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>78</v>
       </c>
       <c r="T48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>24</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_387_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_387_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -1923,10 +1923,10 @@
         <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2511,16 +2511,16 @@
         <v>14</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
         <v>6</v>
@@ -2710,13 +2710,13 @@
         <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X24" t="n">
         <v>7</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>84</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X30" t="n">
         <v>27</v>
@@ -4292,10 +4292,10 @@
         <v>10</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5468,10 +5468,10 @@
         <v>19</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6252,16 +6252,16 @@
         <v>12</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>2</v>
@@ -6784,16 +6784,16 @@
         <v>78</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
         <v>24</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_387_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_387_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2719,14 +2719,14 @@
         <v>4</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3839,14 +3839,14 @@
         <v>8</v>
       </c>
       <c r="X30" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6796,14 +6796,14 @@
         <v>1</v>
       </c>
       <c r="X48" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
